--- a/backtest_runs/20260410_193731/by_symbol/ABL/ABL.xlsx
+++ b/backtest_runs/20260410_193731/by_symbol/ABL/ABL.xlsx
@@ -465,12 +465,12 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>same_side_as_oracle</t>
+          <t>same_side_as_actual</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_diff_oracle_minus_model</t>
+          <t>daily_pnl_diff_actual_minus_model</t>
         </is>
       </c>
       <c r="G1" s="1" t="inlineStr">
@@ -480,7 +480,7 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>suggestion_oracle</t>
+          <t>suggestion_actual</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
@@ -490,7 +490,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>daily_pnl_oracle</t>
+          <t>daily_pnl_actual</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -500,7 +500,7 @@
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>equity_oracle</t>
+          <t>equity_actual</t>
         </is>
       </c>
     </row>
@@ -541,7 +541,7 @@
         <v>-1134.840000000004</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K2" s="2" t="n">
         <v>98865.15999999999</v>
@@ -633,7 +633,7 @@
         <v>-2963.519999999995</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K4" s="2" t="n">
         <v>99588.39999999999</v>
@@ -679,7 +679,7 @@
         <v>-2334.359999999999</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K5" s="2" t="n">
         <v>97254.03999999999</v>
@@ -817,7 +817,7 @@
         <v>-917.2800000000013</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K8" s="2" t="n">
         <v>99823.59999999999</v>
@@ -909,7 +909,7 @@
         <v>-529.2000000000033</v>
       </c>
       <c r="J10" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K10" s="2" t="n">
         <v>99370.83999999998</v>
@@ -1047,7 +1047,7 @@
         <v>-23.51999999999532</v>
       </c>
       <c r="J13" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K13" s="2" t="n">
         <v>99382.59999999999</v>
@@ -1139,7 +1139,7 @@
         <v>-164.6400000000007</v>
       </c>
       <c r="J15" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K15" s="2" t="n">
         <v>100199.92</v>
@@ -1185,7 +1185,7 @@
         <v>-823.1999999999866</v>
       </c>
       <c r="J16" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K16" s="2" t="n">
         <v>99376.72</v>
@@ -1277,7 +1277,7 @@
         <v>-1611.119999999989</v>
       </c>
       <c r="J18" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K18" s="2" t="n">
         <v>98147.8</v>
@@ -1415,7 +1415,7 @@
         <v>-1752.239999999994</v>
       </c>
       <c r="J21" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K21" s="2" t="n">
         <v>100458.64</v>
@@ -1461,7 +1461,7 @@
         <v>-452.760000000006</v>
       </c>
       <c r="J22" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K22" s="2" t="n">
         <v>100005.88</v>
@@ -1507,7 +1507,7 @@
         <v>-5.879999999994652</v>
       </c>
       <c r="J23" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K23" s="2" t="n">
         <v>100000</v>
@@ -1645,7 +1645,7 @@
         <v>-3051.719999999998</v>
       </c>
       <c r="J26" s="2" t="n">
-        <v>-0</v>
+        <v>0</v>
       </c>
       <c r="K26" s="2" t="n">
         <v>105950.56</v>
